--- a/artfynd/A 60584-2019 artfynd.xlsx
+++ b/artfynd/A 60584-2019 artfynd.xlsx
@@ -784,7 +784,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Melina Eberhagen</t>
+          <t>Via Melina Eberhagen</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">

--- a/artfynd/A 60584-2019 artfynd.xlsx
+++ b/artfynd/A 60584-2019 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123156593</v>
       </c>
       <c r="B2" t="n">
-        <v>109250</v>
+        <v>109254</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 60584-2019 artfynd.xlsx
+++ b/artfynd/A 60584-2019 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123156593</v>
       </c>
       <c r="B2" t="n">
-        <v>109254</v>
+        <v>109256</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 60584-2019 artfynd.xlsx
+++ b/artfynd/A 60584-2019 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123156593</v>
       </c>
       <c r="B2" t="n">
-        <v>109256</v>
+        <v>109262</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 60584-2019 artfynd.xlsx
+++ b/artfynd/A 60584-2019 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123156593</v>
       </c>
       <c r="B2" t="n">
-        <v>109262</v>
+        <v>109265</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 60584-2019 artfynd.xlsx
+++ b/artfynd/A 60584-2019 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123156593</v>
       </c>
       <c r="B2" t="n">
-        <v>109265</v>
+        <v>109282</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 60584-2019 artfynd.xlsx
+++ b/artfynd/A 60584-2019 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123156593</v>
       </c>
       <c r="B2" t="n">
-        <v>109282</v>
+        <v>109300</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 60584-2019 artfynd.xlsx
+++ b/artfynd/A 60584-2019 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123156593</v>
       </c>
       <c r="B2" t="n">
-        <v>109300</v>
+        <v>109302</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 60584-2019 artfynd.xlsx
+++ b/artfynd/A 60584-2019 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123156593</v>
       </c>
       <c r="B2" t="n">
-        <v>109302</v>
+        <v>108877</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
